--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125684790</v>
+        <v>125684863</v>
       </c>
       <c r="B2" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387961</v>
+        <v>387954</v>
       </c>
       <c r="R2" t="n">
-        <v>6610980</v>
+        <v>6610912</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, gnag</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125684862</v>
+        <v>125684796</v>
       </c>
       <c r="B3" t="n">
-        <v>92466</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387944</v>
+        <v>387946</v>
       </c>
       <c r="R3" t="n">
-        <v>6611004</v>
+        <v>6610917</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -852,17 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125684796</v>
+        <v>125684862</v>
       </c>
       <c r="B4" t="n">
-        <v>92098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>387946</v>
+        <v>387944</v>
       </c>
       <c r="R4" t="n">
-        <v>6610917</v>
+        <v>6611004</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -959,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Stockbergen, fjolårsfruktkroppar</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125684863</v>
+        <v>125684797</v>
       </c>
       <c r="B5" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>4368</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,7 +1016,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387954</v>
+        <v>387947</v>
       </c>
       <c r="R5" t="n">
         <v>6610912</v>
@@ -1066,17 +1046,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Stockbergen, gnag</t>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125684797</v>
+        <v>125684790</v>
       </c>
       <c r="B6" t="n">
-        <v>92466</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387947</v>
+        <v>387961</v>
       </c>
       <c r="R6" t="n">
-        <v>6610912</v>
+        <v>6610980</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1183,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Stockbergen, fjolårsfruktkroppar</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125684796</v>
       </c>
       <c r="B3" t="n">
-        <v>92152</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125684862</v>
       </c>
       <c r="B4" t="n">
-        <v>92520</v>
+        <v>92527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>125684797</v>
       </c>
       <c r="B5" t="n">
-        <v>92520</v>
+        <v>92527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125684790</v>
       </c>
       <c r="B6" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125684796</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125684862</v>
       </c>
       <c r="B4" t="n">
-        <v>92527</v>
+        <v>92536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>125684797</v>
       </c>
       <c r="B5" t="n">
-        <v>92527</v>
+        <v>92536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125684790</v>
       </c>
       <c r="B6" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125684796</v>
       </c>
       <c r="B3" t="n">
-        <v>92163</v>
+        <v>92167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125684862</v>
       </c>
       <c r="B4" t="n">
-        <v>92536</v>
+        <v>92540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>125684797</v>
       </c>
       <c r="B5" t="n">
-        <v>92536</v>
+        <v>92540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125684790</v>
       </c>
       <c r="B6" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>125684790</v>
       </c>
       <c r="B6" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125684796</v>
       </c>
       <c r="B3" t="n">
-        <v>92167</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125684862</v>
       </c>
       <c r="B4" t="n">
-        <v>92540</v>
+        <v>92542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>125684797</v>
       </c>
       <c r="B5" t="n">
-        <v>92540</v>
+        <v>92542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125684790</v>
       </c>
       <c r="B6" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125684796</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92171</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125684862</v>
       </c>
       <c r="B4" t="n">
-        <v>92542</v>
+        <v>92544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>125684797</v>
       </c>
       <c r="B5" t="n">
-        <v>92542</v>
+        <v>92544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125684790</v>
       </c>
       <c r="B6" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125684796</v>
       </c>
       <c r="B3" t="n">
-        <v>92171</v>
+        <v>92173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125684862</v>
       </c>
       <c r="B4" t="n">
-        <v>92544</v>
+        <v>92546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>125684797</v>
       </c>
       <c r="B5" t="n">
-        <v>92544</v>
+        <v>92546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125684790</v>
       </c>
       <c r="B6" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125684796</v>
       </c>
       <c r="B3" t="n">
-        <v>92173</v>
+        <v>92177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125684862</v>
       </c>
       <c r="B4" t="n">
-        <v>92546</v>
+        <v>92550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>125684797</v>
       </c>
       <c r="B5" t="n">
-        <v>92546</v>
+        <v>92550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125684790</v>
       </c>
       <c r="B6" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>125684790</v>
       </c>
       <c r="B6" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1183,6 +1183,297 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128299778</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92660</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Granmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>387907</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6610896</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Björk, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128299798</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92660</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Granmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>387910</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6610913</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Björk, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128299782</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Granmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>387907</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6610896</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Björk, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128299778</v>
       </c>
       <c r="B7" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128299798</v>
       </c>
       <c r="B8" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>128299782</v>
       </c>
       <c r="B9" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128299778</v>
       </c>
       <c r="B7" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128299798</v>
       </c>
       <c r="B8" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>128299782</v>
       </c>
       <c r="B9" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128299778</v>
+        <v>128299798</v>
       </c>
       <c r="B7" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387907</v>
+        <v>387910</v>
       </c>
       <c r="R7" t="n">
-        <v>6610896</v>
+        <v>6610913</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128299798</v>
+        <v>128299778</v>
       </c>
       <c r="B8" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387910</v>
+        <v>387907</v>
       </c>
       <c r="R8" t="n">
-        <v>6610913</v>
+        <v>6610896</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
         <v>128299782</v>
       </c>
       <c r="B9" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128299798</v>
+        <v>128299778</v>
       </c>
       <c r="B7" t="n">
         <v>92772</v>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387910</v>
+        <v>387907</v>
       </c>
       <c r="R7" t="n">
-        <v>6610913</v>
+        <v>6610896</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128299778</v>
+        <v>128299798</v>
       </c>
       <c r="B8" t="n">
         <v>92772</v>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387907</v>
+        <v>387910</v>
       </c>
       <c r="R8" t="n">
-        <v>6610896</v>
+        <v>6610913</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128299778</v>
       </c>
       <c r="B7" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128299798</v>
       </c>
       <c r="B8" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>128299782</v>
       </c>
       <c r="B9" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128299778</v>
       </c>
       <c r="B7" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128299798</v>
       </c>
       <c r="B8" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>128299782</v>
       </c>
       <c r="B9" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128299778</v>
       </c>
       <c r="B7" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128299798</v>
       </c>
       <c r="B8" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>128299782</v>
       </c>
       <c r="B9" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125684863</v>
+        <v>125684862</v>
       </c>
       <c r="B2" t="n">
-        <v>5196</v>
+        <v>92550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>4368</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387954</v>
+        <v>387944</v>
       </c>
       <c r="R2" t="n">
-        <v>6610912</v>
+        <v>6611004</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Stockbergen, gnag</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125684796</v>
+        <v>125684790</v>
       </c>
       <c r="B3" t="n">
-        <v>92177</v>
+        <v>97230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387946</v>
+        <v>387961</v>
       </c>
       <c r="R3" t="n">
-        <v>6610917</v>
+        <v>6610980</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Stockbergen, fjolårsfruktkroppar</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,603 +876,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>125684862</v>
-      </c>
-      <c r="B4" t="n">
-        <v>92550</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>4368</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dofttaggsvamp</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Hydnellum suaveolens</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Stockbergen, Vrm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>387944</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6611004</v>
-      </c>
-      <c r="S4" t="n">
-        <v>20</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Brunskog</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Lina Lejonberg</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Lina Lejonberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>125684797</v>
-      </c>
-      <c r="B5" t="n">
-        <v>92550</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4368</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dofttaggsvamp</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Hydnellum suaveolens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Stockbergen, Vrm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>387947</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6610912</v>
-      </c>
-      <c r="S5" t="n">
-        <v>20</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Brunskog</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Stockbergen, fjolårsfruktkroppar</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Lina Lejonberg</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Lina Lejonberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>125684790</v>
-      </c>
-      <c r="B6" t="n">
-        <v>97230</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Stockbergen, Vrm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>387961</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6610980</v>
-      </c>
-      <c r="S6" t="n">
-        <v>20</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Brunskog</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Lina Lejonberg</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Lina Lejonberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>128299778</v>
-      </c>
-      <c r="B7" t="n">
-        <v>92812</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>4368</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Dofttaggsvamp</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Hydnellum suaveolens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Granmossen, Vrm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>387907</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6610896</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Brunskog</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Anton Björk, Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>128299798</v>
-      </c>
-      <c r="B8" t="n">
-        <v>92812</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4368</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Dofttaggsvamp</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Hydnellum suaveolens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Granmossen, Vrm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>387910</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6610913</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Brunskog</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Anton Björk, Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>128299782</v>
-      </c>
-      <c r="B9" t="n">
-        <v>92794</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Granmossen, Vrm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>387907</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6610896</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Brunskog</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Anton Björk, Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23085-2024 artfynd.xlsx
+++ b/artfynd/A 23085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125684862</v>
+        <v>123699630</v>
       </c>
       <c r="B2" t="n">
-        <v>92550</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4368</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387944</v>
+        <v>387952</v>
       </c>
       <c r="R2" t="n">
-        <v>6611004</v>
+        <v>6611071</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125684790</v>
+        <v>125684894</v>
       </c>
       <c r="B3" t="n">
-        <v>97230</v>
+        <v>95957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2383</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387961</v>
+        <v>387925</v>
       </c>
       <c r="R3" t="n">
-        <v>6610980</v>
+        <v>6611069</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -842,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -876,6 +871,1024 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125684797</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>387947</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6610912</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125684862</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>387944</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6611004</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125684791</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>387909</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6611050</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125684796</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>387946</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6610917</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118741130</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>387904</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6611026</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118741190</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>387908</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6611036</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125684863</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>387954</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6610912</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stockbergen, gnag</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118741106</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>387904</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6611026</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125684792</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>387896</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6611031</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125684790</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>387961</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6610980</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
